--- a/autohotkey 14.04.25.xlsx
+++ b/autohotkey 14.04.25.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="zz" sheetId="1" r:id="rId1"/>
@@ -11315,12 +11315,28 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -11534,30 +11550,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -15598,7 +15616,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K254"/>
+  <dimension ref="A1:K253"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -16949,49 +16967,49 @@
       <c r="A105" s="19"/>
     </row>
     <row r="106" spans="1:11">
-      <c r="A106" s="19"/>
+      <c r="A106" s="3"/>
     </row>
     <row r="107" spans="1:11">
-      <c r="A107" s="19"/>
+      <c r="A107" s="28"/>
     </row>
     <row r="108" spans="1:11">
-      <c r="A108" s="19"/>
+      <c r="A108" s="28"/>
     </row>
     <row r="109" spans="1:11">
-      <c r="A109" s="19"/>
+      <c r="A109" s="28"/>
     </row>
     <row r="110" spans="1:11">
-      <c r="A110" s="19"/>
+      <c r="A110" s="28"/>
     </row>
     <row r="111" spans="1:11">
-      <c r="A111" s="19"/>
+      <c r="A111" s="27"/>
     </row>
     <row r="112" spans="1:11">
-      <c r="A112" s="19"/>
+      <c r="A112" s="27"/>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="19"/>
+      <c r="A113" s="27"/>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="19"/>
+      <c r="A114" s="27"/>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="19"/>
+      <c r="A115" s="27"/>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="19"/>
+      <c r="A116" s="27"/>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="19"/>
+      <c r="A117" s="27"/>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="19"/>
+      <c r="A118" s="27"/>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="19"/>
+      <c r="A119" s="27"/>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="19"/>
+      <c r="A120" s="27"/>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="19"/>
@@ -17026,907 +17044,905 @@
     <row r="131" spans="1:7">
       <c r="A131" s="19"/>
     </row>
-    <row r="132" spans="1:7">
-      <c r="A132" s="19"/>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
+        <v>891</v>
+      </c>
+      <c r="C133" t="s">
+        <v>910</v>
+      </c>
+      <c r="G133" t="s">
+        <v>853</v>
+      </c>
     </row>
     <row r="134" spans="1:7">
-      <c r="A134" t="s">
-        <v>891</v>
-      </c>
       <c r="C134" t="s">
-        <v>910</v>
-      </c>
-      <c r="G134" t="s">
-        <v>853</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:7">
+      <c r="A135" t="s">
+        <v>892</v>
+      </c>
       <c r="C135" t="s">
-        <v>10</v>
+        <v>911</v>
+      </c>
+      <c r="G135" t="s">
+        <v>855</v>
       </c>
     </row>
     <row r="136" spans="1:7">
-      <c r="A136" t="s">
-        <v>892</v>
-      </c>
       <c r="C136" t="s">
-        <v>911</v>
-      </c>
-      <c r="G136" t="s">
-        <v>855</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:7">
+      <c r="A137" t="s">
+        <v>893</v>
+      </c>
       <c r="C137" t="s">
-        <v>10</v>
+        <v>912</v>
+      </c>
+      <c r="G137" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="138" spans="1:7">
-      <c r="A138" t="s">
-        <v>893</v>
-      </c>
       <c r="C138" t="s">
-        <v>912</v>
-      </c>
-      <c r="G138" t="s">
-        <v>857</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:7">
+      <c r="A139" t="s">
+        <v>894</v>
+      </c>
       <c r="C139" t="s">
-        <v>10</v>
+        <v>913</v>
+      </c>
+      <c r="G139" t="s">
+        <v>859</v>
       </c>
     </row>
     <row r="140" spans="1:7">
-      <c r="A140" t="s">
-        <v>894</v>
-      </c>
       <c r="C140" t="s">
-        <v>913</v>
-      </c>
-      <c r="G140" t="s">
-        <v>859</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7">
+      <c r="A141" t="s">
+        <v>895</v>
+      </c>
       <c r="C141" t="s">
-        <v>10</v>
+        <v>914</v>
+      </c>
+      <c r="G141" t="s">
+        <v>861</v>
       </c>
     </row>
     <row r="142" spans="1:7">
-      <c r="A142" t="s">
-        <v>895</v>
-      </c>
       <c r="C142" t="s">
-        <v>914</v>
-      </c>
-      <c r="G142" t="s">
-        <v>861</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:7">
+      <c r="A143" t="s">
+        <v>896</v>
+      </c>
       <c r="C143" t="s">
-        <v>10</v>
+        <v>915</v>
+      </c>
+      <c r="G143" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="144" spans="1:7">
-      <c r="A144" t="s">
-        <v>896</v>
-      </c>
       <c r="C144" t="s">
-        <v>915</v>
-      </c>
-      <c r="G144" t="s">
-        <v>863</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:7">
+      <c r="A145" t="s">
+        <v>897</v>
+      </c>
       <c r="C145" t="s">
-        <v>10</v>
+        <v>916</v>
+      </c>
+      <c r="G145" t="s">
+        <v>865</v>
       </c>
     </row>
     <row r="146" spans="1:7">
-      <c r="A146" t="s">
-        <v>897</v>
-      </c>
       <c r="C146" t="s">
-        <v>916</v>
-      </c>
-      <c r="G146" t="s">
-        <v>865</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:7">
+      <c r="A147" t="s">
+        <v>898</v>
+      </c>
       <c r="C147" t="s">
-        <v>10</v>
+        <v>917</v>
+      </c>
+      <c r="G147" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="148" spans="1:7">
-      <c r="A148" t="s">
-        <v>898</v>
-      </c>
       <c r="C148" t="s">
-        <v>917</v>
-      </c>
-      <c r="G148" t="s">
-        <v>867</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:7">
+      <c r="A149" t="s">
+        <v>899</v>
+      </c>
       <c r="C149" t="s">
-        <v>10</v>
+        <v>918</v>
+      </c>
+      <c r="G149" t="s">
+        <v>869</v>
       </c>
     </row>
     <row r="150" spans="1:7">
-      <c r="A150" t="s">
-        <v>899</v>
-      </c>
       <c r="C150" t="s">
-        <v>918</v>
-      </c>
-      <c r="G150" t="s">
-        <v>869</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:7">
+      <c r="A151" t="s">
+        <v>900</v>
+      </c>
       <c r="C151" t="s">
-        <v>10</v>
+        <v>919</v>
+      </c>
+      <c r="G151" t="s">
+        <v>871</v>
       </c>
     </row>
     <row r="152" spans="1:7">
-      <c r="A152" t="s">
-        <v>900</v>
-      </c>
       <c r="C152" t="s">
-        <v>919</v>
-      </c>
-      <c r="G152" t="s">
-        <v>871</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:7">
+      <c r="A153" t="s">
+        <v>901</v>
+      </c>
       <c r="C153" t="s">
-        <v>10</v>
+        <v>920</v>
+      </c>
+      <c r="G153" t="s">
+        <v>873</v>
       </c>
     </row>
     <row r="154" spans="1:7">
-      <c r="A154" t="s">
-        <v>901</v>
-      </c>
       <c r="C154" t="s">
-        <v>920</v>
-      </c>
-      <c r="G154" t="s">
-        <v>873</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:7">
+      <c r="A155" t="s">
+        <v>902</v>
+      </c>
       <c r="C155" t="s">
-        <v>10</v>
+        <v>921</v>
+      </c>
+      <c r="G155" t="s">
+        <v>875</v>
       </c>
     </row>
     <row r="156" spans="1:7">
-      <c r="A156" t="s">
-        <v>902</v>
-      </c>
       <c r="C156" t="s">
-        <v>921</v>
-      </c>
-      <c r="G156" t="s">
-        <v>875</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:7">
+      <c r="A157" t="s">
+        <v>903</v>
+      </c>
       <c r="C157" t="s">
-        <v>10</v>
+        <v>922</v>
+      </c>
+      <c r="G157" t="s">
+        <v>877</v>
       </c>
     </row>
     <row r="158" spans="1:7">
-      <c r="A158" t="s">
-        <v>903</v>
-      </c>
       <c r="C158" t="s">
-        <v>922</v>
-      </c>
-      <c r="G158" t="s">
-        <v>877</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:7">
+      <c r="A159" t="s">
+        <v>904</v>
+      </c>
       <c r="C159" t="s">
-        <v>10</v>
+        <v>923</v>
+      </c>
+      <c r="G159" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="160" spans="1:7">
-      <c r="A160" t="s">
-        <v>904</v>
-      </c>
       <c r="C160" t="s">
-        <v>923</v>
-      </c>
-      <c r="G160" t="s">
-        <v>879</v>
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>905</v>
+      </c>
       <c r="C161" t="s">
-        <v>10</v>
+        <v>924</v>
+      </c>
+      <c r="G161" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="162" spans="1:7">
-      <c r="A162" t="s">
-        <v>905</v>
-      </c>
       <c r="C162" t="s">
-        <v>924</v>
-      </c>
-      <c r="G162" t="s">
-        <v>881</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>906</v>
+      </c>
       <c r="C163" t="s">
-        <v>10</v>
+        <v>925</v>
+      </c>
+      <c r="G163" t="s">
+        <v>883</v>
       </c>
     </row>
     <row r="164" spans="1:7">
-      <c r="A164" t="s">
-        <v>906</v>
-      </c>
       <c r="C164" t="s">
-        <v>925</v>
-      </c>
-      <c r="G164" t="s">
-        <v>883</v>
+        <v>10</v>
       </c>
     </row>
     <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>907</v>
+      </c>
       <c r="C165" t="s">
-        <v>10</v>
+        <v>926</v>
+      </c>
+      <c r="G165" t="s">
+        <v>885</v>
       </c>
     </row>
     <row r="166" spans="1:7">
-      <c r="A166" t="s">
-        <v>907</v>
-      </c>
       <c r="C166" t="s">
-        <v>926</v>
-      </c>
-      <c r="G166" t="s">
-        <v>885</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>908</v>
+      </c>
       <c r="C167" t="s">
-        <v>10</v>
+        <v>927</v>
+      </c>
+      <c r="G167" t="s">
+        <v>887</v>
       </c>
     </row>
     <row r="168" spans="1:7">
-      <c r="A168" t="s">
-        <v>908</v>
-      </c>
       <c r="C168" t="s">
-        <v>927</v>
-      </c>
-      <c r="G168" t="s">
-        <v>887</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>909</v>
+      </c>
       <c r="C169" t="s">
-        <v>10</v>
+        <v>928</v>
+      </c>
+      <c r="G169" t="s">
+        <v>889</v>
       </c>
     </row>
     <row r="170" spans="1:7">
-      <c r="A170" t="s">
-        <v>909</v>
-      </c>
       <c r="C170" t="s">
-        <v>928</v>
-      </c>
-      <c r="G170" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
-      <c r="C171" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C173" t="s">
+        <v>2160</v>
+      </c>
+      <c r="G173" t="s">
+        <v>2116</v>
       </c>
     </row>
     <row r="174" spans="1:7">
-      <c r="A174" t="s">
-        <v>2131</v>
-      </c>
       <c r="C174" t="s">
-        <v>2160</v>
-      </c>
-      <c r="G174" t="s">
-        <v>2116</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:7">
+      <c r="A175" t="s">
+        <v>2132</v>
+      </c>
       <c r="C175" t="s">
-        <v>10</v>
+        <v>2161</v>
+      </c>
+      <c r="G175" t="s">
+        <v>2118</v>
       </c>
     </row>
     <row r="176" spans="1:7">
-      <c r="A176" t="s">
-        <v>2132</v>
-      </c>
       <c r="C176" t="s">
-        <v>2161</v>
-      </c>
-      <c r="G176" t="s">
-        <v>2118</v>
+        <v>10</v>
       </c>
     </row>
     <row r="177" spans="1:7">
+      <c r="A177" t="s">
+        <v>2133</v>
+      </c>
       <c r="C177" t="s">
-        <v>10</v>
+        <v>2162</v>
+      </c>
+      <c r="G177" t="s">
+        <v>2120</v>
       </c>
     </row>
     <row r="178" spans="1:7">
-      <c r="A178" t="s">
-        <v>2133</v>
-      </c>
       <c r="C178" t="s">
-        <v>2162</v>
-      </c>
-      <c r="G178" t="s">
-        <v>2120</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:7">
+      <c r="A179" t="s">
+        <v>2134</v>
+      </c>
       <c r="C179" t="s">
-        <v>10</v>
+        <v>2163</v>
+      </c>
+      <c r="G179" t="s">
+        <v>2122</v>
       </c>
     </row>
     <row r="180" spans="1:7">
-      <c r="A180" t="s">
-        <v>2134</v>
-      </c>
       <c r="C180" t="s">
-        <v>2163</v>
-      </c>
-      <c r="G180" t="s">
-        <v>2122</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:7">
+      <c r="A181" t="s">
+        <v>2135</v>
+      </c>
       <c r="C181" t="s">
-        <v>10</v>
+        <v>2164</v>
+      </c>
+      <c r="G181" t="s">
+        <v>2124</v>
       </c>
     </row>
     <row r="182" spans="1:7">
-      <c r="A182" t="s">
-        <v>2135</v>
-      </c>
       <c r="C182" t="s">
-        <v>2164</v>
-      </c>
-      <c r="G182" t="s">
-        <v>2124</v>
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:7">
+      <c r="A183" t="s">
+        <v>2136</v>
+      </c>
       <c r="C183" t="s">
-        <v>10</v>
+        <v>2165</v>
+      </c>
+      <c r="G183" t="s">
+        <v>2126</v>
       </c>
     </row>
     <row r="184" spans="1:7">
-      <c r="A184" t="s">
-        <v>2136</v>
-      </c>
       <c r="C184" t="s">
-        <v>2165</v>
-      </c>
-      <c r="G184" t="s">
-        <v>2126</v>
+        <v>10</v>
       </c>
     </row>
     <row r="185" spans="1:7">
+      <c r="A185" t="s">
+        <v>2137</v>
+      </c>
       <c r="C185" t="s">
-        <v>10</v>
+        <v>2166</v>
+      </c>
+      <c r="G185" t="s">
+        <v>2128</v>
       </c>
     </row>
     <row r="186" spans="1:7">
-      <c r="A186" t="s">
-        <v>2137</v>
-      </c>
       <c r="C186" t="s">
-        <v>2166</v>
-      </c>
-      <c r="G186" t="s">
-        <v>2128</v>
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:7">
+      <c r="A187" t="s">
+        <v>2138</v>
+      </c>
       <c r="C187" t="s">
-        <v>10</v>
+        <v>2167</v>
+      </c>
+      <c r="G187" t="s">
+        <v>2130</v>
       </c>
     </row>
     <row r="188" spans="1:7">
-      <c r="A188" t="s">
-        <v>2138</v>
-      </c>
       <c r="C188" t="s">
-        <v>2167</v>
-      </c>
-      <c r="G188" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7">
-      <c r="C189" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C190" t="s">
+        <v>2168</v>
+      </c>
+      <c r="G190" t="s">
+        <v>2140</v>
       </c>
     </row>
     <row r="191" spans="1:7">
-      <c r="A191" t="s">
-        <v>2153</v>
-      </c>
       <c r="C191" t="s">
-        <v>2168</v>
-      </c>
-      <c r="G191" t="s">
-        <v>2140</v>
+        <v>10</v>
       </c>
     </row>
     <row r="192" spans="1:7">
+      <c r="A192" t="s">
+        <v>2154</v>
+      </c>
       <c r="C192" t="s">
-        <v>10</v>
+        <v>2169</v>
+      </c>
+      <c r="G192" t="s">
+        <v>2142</v>
       </c>
     </row>
     <row r="193" spans="1:7">
-      <c r="A193" t="s">
-        <v>2154</v>
-      </c>
       <c r="C193" t="s">
-        <v>2169</v>
-      </c>
-      <c r="G193" t="s">
-        <v>2142</v>
+        <v>10</v>
       </c>
     </row>
     <row r="194" spans="1:7">
+      <c r="A194" t="s">
+        <v>2155</v>
+      </c>
       <c r="C194" t="s">
-        <v>10</v>
+        <v>2170</v>
+      </c>
+      <c r="G194" t="s">
+        <v>2144</v>
       </c>
     </row>
     <row r="195" spans="1:7">
-      <c r="A195" t="s">
-        <v>2155</v>
-      </c>
       <c r="C195" t="s">
-        <v>2170</v>
-      </c>
-      <c r="G195" t="s">
-        <v>2144</v>
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:7">
+      <c r="A196" t="s">
+        <v>2156</v>
+      </c>
       <c r="C196" t="s">
-        <v>10</v>
+        <v>2171</v>
+      </c>
+      <c r="G196" t="s">
+        <v>2146</v>
       </c>
     </row>
     <row r="197" spans="1:7">
-      <c r="A197" t="s">
-        <v>2156</v>
-      </c>
       <c r="C197" t="s">
-        <v>2171</v>
-      </c>
-      <c r="G197" t="s">
-        <v>2146</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:7">
+      <c r="A198" t="s">
+        <v>2157</v>
+      </c>
       <c r="C198" t="s">
-        <v>10</v>
+        <v>2172</v>
+      </c>
+      <c r="G198" t="s">
+        <v>2148</v>
       </c>
     </row>
     <row r="199" spans="1:7">
-      <c r="A199" t="s">
-        <v>2157</v>
-      </c>
       <c r="C199" t="s">
-        <v>2172</v>
-      </c>
-      <c r="G199" t="s">
-        <v>2148</v>
+        <v>10</v>
       </c>
     </row>
     <row r="200" spans="1:7">
+      <c r="A200" t="s">
+        <v>2158</v>
+      </c>
       <c r="C200" t="s">
-        <v>10</v>
+        <v>2173</v>
+      </c>
+      <c r="G200" t="s">
+        <v>2150</v>
       </c>
     </row>
     <row r="201" spans="1:7">
-      <c r="A201" t="s">
-        <v>2158</v>
-      </c>
       <c r="C201" t="s">
-        <v>2173</v>
-      </c>
-      <c r="G201" t="s">
-        <v>2150</v>
+        <v>10</v>
       </c>
     </row>
     <row r="202" spans="1:7">
+      <c r="A202" t="s">
+        <v>2159</v>
+      </c>
       <c r="C202" t="s">
-        <v>10</v>
+        <v>2174</v>
+      </c>
+      <c r="G202" t="s">
+        <v>2152</v>
       </c>
     </row>
     <row r="203" spans="1:7">
-      <c r="A203" t="s">
-        <v>2159</v>
-      </c>
       <c r="C203" t="s">
-        <v>2174</v>
-      </c>
-      <c r="G203" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7">
-      <c r="C204" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C206" t="s">
+        <v>2201</v>
+      </c>
+      <c r="G206" t="s">
+        <v>2186</v>
       </c>
     </row>
     <row r="207" spans="1:7">
-      <c r="A207" t="s">
+      <c r="C207" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C208" t="s">
+        <v>2202</v>
+      </c>
+      <c r="G208" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="C209" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C210" t="s">
+        <v>2203</v>
+      </c>
+      <c r="G210" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="C211" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C212" t="s">
+        <v>2204</v>
+      </c>
+      <c r="G212" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="C213" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C214" t="s">
+        <v>2205</v>
+      </c>
+      <c r="G214" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="C215" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C216" t="s">
+        <v>2206</v>
+      </c>
+      <c r="G216" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="C217" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C218" t="s">
+        <v>2207</v>
+      </c>
+      <c r="G218" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="C219" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C220" t="s">
+        <v>2208</v>
+      </c>
+      <c r="G220" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="C221" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" t="s">
         <v>2177</v>
       </c>
-      <c r="C207" t="s">
+      <c r="C223" t="s">
         <v>2201</v>
       </c>
-      <c r="G207" t="s">
+      <c r="G223" t="s">
         <v>2186</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
-      <c r="C208" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7">
-      <c r="A209" t="s">
+    <row r="224" spans="1:7">
+      <c r="C224" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" t="s">
         <v>2178</v>
       </c>
-      <c r="C209" t="s">
+      <c r="C225" t="s">
         <v>2202</v>
       </c>
-      <c r="G209" t="s">
+      <c r="G225" t="s">
         <v>2188</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
-      <c r="C210" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7">
-      <c r="A211" t="s">
+    <row r="226" spans="1:7">
+      <c r="C226" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" t="s">
         <v>2179</v>
       </c>
-      <c r="C211" t="s">
+      <c r="C227" t="s">
         <v>2203</v>
       </c>
-      <c r="G211" t="s">
+      <c r="G227" t="s">
         <v>2190</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
-      <c r="C212" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7">
-      <c r="A213" t="s">
+    <row r="228" spans="1:7">
+      <c r="C228" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" t="s">
         <v>2180</v>
       </c>
-      <c r="C213" t="s">
+      <c r="C229" t="s">
         <v>2204</v>
       </c>
-      <c r="G213" t="s">
+      <c r="G229" t="s">
         <v>2192</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
-      <c r="C214" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7">
-      <c r="A215" t="s">
+    <row r="230" spans="1:7">
+      <c r="C230" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" t="s">
         <v>2181</v>
       </c>
-      <c r="C215" t="s">
+      <c r="C231" t="s">
         <v>2205</v>
       </c>
-      <c r="G215" t="s">
+      <c r="G231" t="s">
         <v>2194</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
-      <c r="C216" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7">
-      <c r="A217" t="s">
+    <row r="232" spans="1:7">
+      <c r="C232" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" t="s">
         <v>2182</v>
       </c>
-      <c r="C217" t="s">
+      <c r="C233" t="s">
         <v>2206</v>
       </c>
-      <c r="G217" t="s">
+      <c r="G233" t="s">
         <v>2196</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
-      <c r="C218" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7">
-      <c r="A219" t="s">
+    <row r="234" spans="1:7">
+      <c r="C234" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" t="s">
         <v>2183</v>
       </c>
-      <c r="C219" t="s">
+      <c r="C235" t="s">
         <v>2207</v>
       </c>
-      <c r="G219" t="s">
+      <c r="G235" t="s">
         <v>2198</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
-      <c r="C220" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7">
-      <c r="A221" t="s">
+    <row r="236" spans="1:7">
+      <c r="C236" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" t="s">
         <v>2184</v>
       </c>
-      <c r="C221" t="s">
+      <c r="C237" t="s">
         <v>2208</v>
       </c>
-      <c r="G221" t="s">
+      <c r="G237" t="s">
         <v>2200</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
-      <c r="C222" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7">
-      <c r="A224" t="s">
-        <v>2177</v>
-      </c>
-      <c r="C224" t="s">
-        <v>2201</v>
-      </c>
-      <c r="G224" t="s">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7">
-      <c r="C225" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7">
-      <c r="A226" t="s">
-        <v>2178</v>
-      </c>
-      <c r="C226" t="s">
-        <v>2202</v>
-      </c>
-      <c r="G226" t="s">
-        <v>2188</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7">
-      <c r="C227" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7">
-      <c r="A228" t="s">
-        <v>2179</v>
-      </c>
-      <c r="C228" t="s">
-        <v>2203</v>
-      </c>
-      <c r="G228" t="s">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7">
-      <c r="C229" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7">
-      <c r="A230" t="s">
-        <v>2180</v>
-      </c>
-      <c r="C230" t="s">
-        <v>2204</v>
-      </c>
-      <c r="G230" t="s">
-        <v>2192</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7">
-      <c r="C231" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7">
-      <c r="A232" t="s">
-        <v>2181</v>
-      </c>
-      <c r="C232" t="s">
-        <v>2205</v>
-      </c>
-      <c r="G232" t="s">
-        <v>2194</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7">
-      <c r="C233" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7">
-      <c r="A234" t="s">
-        <v>2182</v>
-      </c>
-      <c r="C234" t="s">
-        <v>2206</v>
-      </c>
-      <c r="G234" t="s">
-        <v>2196</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7">
-      <c r="C235" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7">
-      <c r="A236" t="s">
-        <v>2183</v>
-      </c>
-      <c r="C236" t="s">
-        <v>2207</v>
-      </c>
-      <c r="G236" t="s">
-        <v>2198</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7">
-      <c r="C237" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="238" spans="1:7">
-      <c r="A238" t="s">
-        <v>2184</v>
-      </c>
       <c r="C238" t="s">
-        <v>2208</v>
-      </c>
-      <c r="G238" t="s">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7">
-      <c r="C239" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242" t="s">
+        <v>2852</v>
+      </c>
+      <c r="C242" t="s">
+        <v>2858</v>
+      </c>
+      <c r="G242" t="s">
+        <v>2841</v>
       </c>
     </row>
     <row r="243" spans="1:7">
-      <c r="A243" t="s">
-        <v>2852</v>
-      </c>
       <c r="C243" t="s">
-        <v>2858</v>
-      </c>
-      <c r="G243" t="s">
-        <v>2841</v>
+        <v>10</v>
       </c>
     </row>
     <row r="244" spans="1:7">
+      <c r="A244" t="s">
+        <v>2853</v>
+      </c>
       <c r="C244" t="s">
-        <v>10</v>
+        <v>2859</v>
+      </c>
+      <c r="G244" t="s">
+        <v>2843</v>
       </c>
     </row>
     <row r="245" spans="1:7">
-      <c r="A245" t="s">
-        <v>2853</v>
-      </c>
       <c r="C245" t="s">
-        <v>2859</v>
-      </c>
-      <c r="G245" t="s">
-        <v>2843</v>
+        <v>10</v>
       </c>
     </row>
     <row r="246" spans="1:7">
+      <c r="A246" t="s">
+        <v>2854</v>
+      </c>
       <c r="C246" t="s">
-        <v>10</v>
+        <v>2860</v>
+      </c>
+      <c r="G246" t="s">
+        <v>2845</v>
       </c>
     </row>
     <row r="247" spans="1:7">
-      <c r="A247" t="s">
-        <v>2854</v>
-      </c>
       <c r="C247" t="s">
-        <v>2860</v>
-      </c>
-      <c r="G247" t="s">
-        <v>2845</v>
+        <v>10</v>
       </c>
     </row>
     <row r="248" spans="1:7">
+      <c r="A248" t="s">
+        <v>2855</v>
+      </c>
       <c r="C248" t="s">
-        <v>10</v>
+        <v>2861</v>
+      </c>
+      <c r="G248" t="s">
+        <v>2847</v>
       </c>
     </row>
     <row r="249" spans="1:7">
-      <c r="A249" t="s">
-        <v>2855</v>
-      </c>
       <c r="C249" t="s">
-        <v>2861</v>
-      </c>
-      <c r="G249" t="s">
-        <v>2847</v>
+        <v>10</v>
       </c>
     </row>
     <row r="250" spans="1:7">
+      <c r="A250" t="s">
+        <v>2856</v>
+      </c>
       <c r="C250" t="s">
-        <v>10</v>
+        <v>2862</v>
+      </c>
+      <c r="G250" t="s">
+        <v>2849</v>
       </c>
     </row>
     <row r="251" spans="1:7">
-      <c r="A251" t="s">
-        <v>2856</v>
-      </c>
       <c r="C251" t="s">
-        <v>2862</v>
-      </c>
-      <c r="G251" t="s">
-        <v>2849</v>
+        <v>10</v>
       </c>
     </row>
     <row r="252" spans="1:7">
+      <c r="A252" t="s">
+        <v>2857</v>
+      </c>
       <c r="C252" t="s">
-        <v>10</v>
+        <v>2863</v>
+      </c>
+      <c r="G252" t="s">
+        <v>2851</v>
       </c>
     </row>
     <row r="253" spans="1:7">
-      <c r="A253" t="s">
-        <v>2857</v>
-      </c>
       <c r="C253" t="s">
-        <v>2863</v>
-      </c>
-      <c r="G253" t="s">
-        <v>2851</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7">
-      <c r="C254" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/autohotkey 14.04.25.xlsx
+++ b/autohotkey 14.04.25.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="11"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="zz" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5562" uniqueCount="3627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5563" uniqueCount="3628">
   <si>
     <t>Здравей,</t>
   </si>
@@ -11309,6 +11309,9 @@
   </si>
   <si>
     <t>https://myspeedy.speedy.bg/consignments/new?template=59156e4a-563f-46ab-96c3-d8a137b3e5e4#</t>
+  </si>
+  <si>
+    <t>::qq24::python -c "import sys; print(sys.executable)"</t>
   </si>
 </sst>
 </file>
@@ -26448,6 +26451,11 @@
         <v>3612</v>
       </c>
     </row>
+    <row r="172" spans="1:4">
+      <c r="A172" t="s">
+        <v>3627</v>
+      </c>
+    </row>
     <row r="174" spans="1:4">
       <c r="A174" s="3" t="s">
         <v>3052</v>

--- a/autohotkey 14.04.25.xlsx
+++ b/autohotkey 14.04.25.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="zz" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5563" uniqueCount="3628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5578" uniqueCount="3643">
   <si>
     <t>Здравей,</t>
   </si>
@@ -11312,6 +11312,51 @@
   </si>
   <si>
     <t>::qq24::python -c "import sys; print(sys.executable)"</t>
+  </si>
+  <si>
+    <t>xx120</t>
+  </si>
+  <si>
+    <t>1SFA611130R1108</t>
+  </si>
+  <si>
+    <t>Бутон двоен светещ ABB MPD1-11C</t>
+  </si>
+  <si>
+    <t>xx121</t>
+  </si>
+  <si>
+    <t>xx122</t>
+  </si>
+  <si>
+    <t>xx123</t>
+  </si>
+  <si>
+    <t>1SFA611605R1100</t>
+  </si>
+  <si>
+    <t>Държач ABB MCBH-00</t>
+  </si>
+  <si>
+    <t>1SFA611610R1001</t>
+  </si>
+  <si>
+    <t>1SFA611610R1010</t>
+  </si>
+  <si>
+    <t>xx124</t>
+  </si>
+  <si>
+    <t>1SFA611621R1075</t>
+  </si>
+  <si>
+    <t>Контактен блок ABB MCB-10</t>
+  </si>
+  <si>
+    <t>Контактен блок ABB MCB-01</t>
+  </si>
+  <si>
+    <t>Лампов блок ABB MLBL-07W с LED</t>
   </si>
 </sst>
 </file>
@@ -37404,7 +37449,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
@@ -38550,12 +38595,12 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:8">
       <c r="B193" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:8">
       <c r="A195" t="s">
         <v>1848</v>
       </c>
@@ -38566,75 +38611,150 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:8">
       <c r="B196" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="198" spans="1:8">
+      <c r="A198" t="s">
+        <v>3054</v>
+      </c>
+      <c r="B198" t="s">
+        <v>3056</v>
+      </c>
+      <c r="E198">
+        <v>617676</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="B199" t="s">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="E199">
-        <v>617676</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5">
+        <v>89117</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>3055</v>
+        <v>3110</v>
       </c>
       <c r="B200" t="s">
-        <v>3057</v>
+        <v>3113</v>
       </c>
       <c r="E200">
-        <v>89117</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5">
+        <v>9215400007</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>3110</v>
+        <v>3111</v>
       </c>
       <c r="B201" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="E201">
-        <v>9215400007</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5">
+        <v>9215400006</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>3111</v>
+        <v>3059</v>
       </c>
       <c r="B202" t="s">
-        <v>3112</v>
-      </c>
-      <c r="E202">
-        <v>9215400006</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5">
-      <c r="A203" t="s">
-        <v>3059</v>
-      </c>
-      <c r="B203" t="s">
         <v>3060</v>
       </c>
-      <c r="E203" t="s">
+      <c r="E202" t="s">
         <v>3058</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
-      <c r="A205" t="s">
+    <row r="204" spans="1:8">
+      <c r="A204" t="s">
         <v>3231</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B204" t="s">
         <v>3232</v>
       </c>
-      <c r="E205" t="e">
+      <c r="E204" t="e">
         <v>#N/A</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206" t="s">
+        <v>3628</v>
+      </c>
+      <c r="B206" t="s">
+        <v>3629</v>
+      </c>
+      <c r="D206" t="s">
+        <v>3630</v>
+      </c>
+      <c r="H206" t="str">
+        <f>"::"&amp;A206&amp;"::"&amp;B206</f>
+        <v>::xx120::1SFA611130R1108</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" t="s">
+        <v>3631</v>
+      </c>
+      <c r="B207" t="s">
+        <v>3634</v>
+      </c>
+      <c r="D207" t="s">
+        <v>3635</v>
+      </c>
+      <c r="H207" t="str">
+        <f>"::"&amp;A207&amp;"::"&amp;B207</f>
+        <v>::xx121::1SFA611605R1100</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" t="s">
+        <v>3632</v>
+      </c>
+      <c r="B208" t="s">
+        <v>3636</v>
+      </c>
+      <c r="D208" t="s">
+        <v>3640</v>
+      </c>
+      <c r="H208" t="str">
+        <f t="shared" ref="H208:H210" si="0">"::"&amp;A208&amp;"::"&amp;B208</f>
+        <v>::xx122::1SFA611610R1001</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" t="s">
+        <v>3633</v>
+      </c>
+      <c r="B209" t="s">
+        <v>3637</v>
+      </c>
+      <c r="D209" t="s">
+        <v>3641</v>
+      </c>
+      <c r="H209" t="str">
+        <f t="shared" si="0"/>
+        <v>::xx123::1SFA611610R1010</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" t="s">
+        <v>3638</v>
+      </c>
+      <c r="B210" t="s">
+        <v>3639</v>
+      </c>
+      <c r="D210" t="s">
+        <v>3642</v>
+      </c>
+      <c r="H210" t="str">
+        <f t="shared" si="0"/>
+        <v>::xx124::1SFA611621R1075</v>
       </c>
     </row>
   </sheetData>
